--- a/docs/deliverables/out/Drop-1_Transactional/TestPlans/BIBS_TestPlan_BRD-06_Renewal_v1.1.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/TestPlans/BIBS_TestPlan_BRD-06_Renewal_v1.1.xlsx
@@ -2096,7 +2096,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Role code and name (and demo user for built BRDs)</t>
+          <t>Role code and name (and SIT/UAT user for built BRDs)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Demo seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
+          <t>Seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -50036,7 +50036,7 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Loaded by the migration mock on SIT (BRD-13 objects P01, R06); tracker prepared by the test lead from template RNW_RA_ALREADY_SENT (masked)</t>
+          <t>Loaded by the trial migration on SIT (BRD-13 objects P01, R06); tracker prepared by the test lead from template RNW_RA_ALREADY_SENT (masked)</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
@@ -50061,7 +50061,7 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Code map of the migration mock (maintained by MBS / TSU); package versions of the BRD-3 catalogue on SIT</t>
+          <t>Code map of the trial migration (maintained by MBS / TSU); package versions of the BRD-3 catalogue on SIT</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
